--- a/data/LISST_data/raw/LaJara_LISST_GSD_Summer2023.xlsx
+++ b/data/LISST_data/raw/LaJara_LISST_GSD_Summer2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\La_Jara\GSD\Water Samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\hysteresis\data\LISST_data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616D03CE-313B-4F2A-BB08-4F2EA34058E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7427C8E4-93D4-40FB-B599-B5F864F6213B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25200" windowHeight="15150" activeTab="4" xr2:uid="{5952B5DA-6B13-43D1-9193-1BE03F62DE4B}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5952B5DA-6B13-43D1-9193-1BE03F62DE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="&quot;Storm&quot; 4" sheetId="2" r:id="rId1"/>
@@ -40,15 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="503">
   <si>
     <t>Dilutions</t>
   </si>
   <si>
     <t>Transmissivity (%)</t>
-  </si>
-  <si>
-    <t>Concentration (mg/L)</t>
   </si>
   <si>
     <t>D50</t>
@@ -1959,7 +1956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2027,7 +2024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2040,22 +2037,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2067,39 +2055,26 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2154,22 +2129,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2527,45 +2493,45 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="75"/>
+      <c r="A2" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="64"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>4</v>
-      </c>
       <c r="M2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="57" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q2" s="31" t="s">
-        <v>496</v>
+        <v>2</v>
+      </c>
+      <c r="N2" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" s="66"/>
+      <c r="P2" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>495</v>
       </c>
       <c r="R2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="13">
         <v>45136.636111111111</v>
@@ -2583,31 +2549,31 @@
         <v>57.67</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I3" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="J3" s="16" t="s">
         <v>492</v>
       </c>
-      <c r="J3" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="K3" s="49" t="s">
-        <v>491</v>
-      </c>
-      <c r="M3" s="72">
+      <c r="K3" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="M3" s="37">
         <f>AVERAGE(F3:F5)</f>
         <v>58.623333333333335</v>
       </c>
-      <c r="N3" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="55">
+      <c r="N3" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="47">
         <v>45136.636111111111</v>
       </c>
-      <c r="P3" s="56">
+      <c r="P3" s="48">
         <f>AVERAGE(H4:H6)</f>
         <v>327.45333333333332</v>
       </c>
@@ -2617,7 +2583,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="14">
         <v>45136.636111111111</v>
@@ -2635,9 +2601,9 @@
         <v>58.77</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="H4" s="45">
+        <v>123</v>
+      </c>
+      <c r="H4" s="39">
         <f>K4/(1-($J$4/$I$4))</f>
         <v>320.83999999999997</v>
       </c>
@@ -2650,17 +2616,17 @@
       <c r="K4" s="2">
         <v>240.63</v>
       </c>
-      <c r="M4" s="72">
+      <c r="M4" s="37">
         <f>AVERAGE(F6:F8)</f>
         <v>43.326666666666661</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="52">
+        <v>73</v>
+      </c>
+      <c r="O4" s="44">
         <v>45136.646527777775</v>
       </c>
-      <c r="P4" s="53">
+      <c r="P4" s="45">
         <f>AVERAGE(H10:H12)</f>
         <v>241.80933333333334</v>
       </c>
@@ -2670,7 +2636,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="14">
         <v>45136.636111111111</v>
@@ -2688,7 +2654,7 @@
         <v>59.43</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" s="3">
         <f>K5/(1-($J$4/$I$4))</f>
@@ -2699,17 +2665,17 @@
       <c r="K5" s="5">
         <v>246.07</v>
       </c>
-      <c r="M5" s="72">
+      <c r="M5" s="37">
         <f>AVERAGE(F9:F12)</f>
         <v>31.197499999999998</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="52">
+        <v>49</v>
+      </c>
+      <c r="O5" s="44">
         <v>45136.656944444447</v>
       </c>
-      <c r="P5" s="53">
+      <c r="P5" s="45">
         <f>AVERAGE(E9:E12)</f>
         <v>158.52499999999998</v>
       </c>
@@ -2719,7 +2685,7 @@
     </row>
     <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="14">
         <v>45136.646527777775</v>
@@ -2737,28 +2703,28 @@
         <v>45.04</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="H6" s="47">
+        <v>130</v>
+      </c>
+      <c r="H6" s="40">
         <f>K6/(1-($J$4/$I$4))</f>
         <v>333.42666666666668</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="50">
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="42">
         <v>250.07</v>
       </c>
-      <c r="M6" s="72">
+      <c r="M6" s="37">
         <f>AVERAGE(F13:F17)</f>
         <v>47.942</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O6" s="52">
+        <v>54</v>
+      </c>
+      <c r="O6" s="44">
         <v>45136.667361111111</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="45">
         <f>AVERAGE(E13:E17)</f>
         <v>132.47200000000001</v>
       </c>
@@ -2768,7 +2734,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="14">
         <v>45136.646527777775</v>
@@ -2786,19 +2752,19 @@
         <v>41.12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="M7" s="72">
+        <v>131</v>
+      </c>
+      <c r="M7" s="37">
         <f>AVERAGE(F18:F20)</f>
         <v>37.686666666666667</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" s="52">
+        <v>58</v>
+      </c>
+      <c r="O7" s="44">
         <v>45136.677777777775</v>
       </c>
-      <c r="P7" s="53">
+      <c r="P7" s="45">
         <f>AVERAGE(E18:E20)</f>
         <v>98.909999999999982</v>
       </c>
@@ -2808,7 +2774,7 @@
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="14">
         <v>45136.646527777775</v>
@@ -2826,19 +2792,19 @@
         <v>43.82</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="M8" s="72">
+        <v>132</v>
+      </c>
+      <c r="M8" s="37">
         <f>AVERAGE(F21:F23)</f>
         <v>40.83</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="52">
+        <v>60</v>
+      </c>
+      <c r="O8" s="44">
         <v>45136.688194444447</v>
       </c>
-      <c r="P8" s="53">
+      <c r="P8" s="45">
         <f>AVERAGE(E21:E23)</f>
         <v>90.356666666666669</v>
       </c>
@@ -2848,7 +2814,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="14">
         <v>45136.656944444447</v>
@@ -2866,28 +2832,28 @@
         <v>29.63</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="H9" s="45" t="s">
-        <v>74</v>
+        <v>133</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>73</v>
       </c>
       <c r="I9" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>492</v>
       </c>
-      <c r="J9" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="K9" s="46" t="s">
-        <v>491</v>
-      </c>
-      <c r="M9" s="72">
+      <c r="K9" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="M9" s="37">
         <f>AVERAGE(F24:F28)</f>
         <v>63.395999999999994</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9" s="52">
+        <v>62</v>
+      </c>
+      <c r="O9" s="44">
         <v>45136.698611111111</v>
       </c>
       <c r="P9" s="4">
@@ -2900,7 +2866,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="14">
         <v>45136.656944444447</v>
@@ -2918,7 +2884,7 @@
         <v>32.83</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="3">
         <f>K10/(1-($J$10/$I$10))</f>
@@ -2933,14 +2899,14 @@
       <c r="K10" s="5">
         <v>220.47</v>
       </c>
-      <c r="M10" s="72">
+      <c r="M10" s="37">
         <f>AVERAGE(F29:F34)</f>
         <v>53.681666666666672</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="O10" s="52">
+        <v>64</v>
+      </c>
+      <c r="O10" s="44">
         <v>45136.709027777775</v>
       </c>
       <c r="P10" s="4">
@@ -2948,12 +2914,12 @@
         <v>69.045000000000002</v>
       </c>
       <c r="Q10" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="14">
         <v>45136.656944444447</v>
@@ -2971,25 +2937,25 @@
         <v>30.36</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" ref="H11:H12" si="0">K11/(1-($J$10/$I$10))</f>
         <v>232.309</v>
       </c>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
       <c r="K11" s="5">
         <v>211.19</v>
       </c>
-      <c r="M11" s="72">
+      <c r="M11" s="37">
         <f>AVERAGE(F35:F39)</f>
         <v>50.762</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O11" s="52">
+        <v>66</v>
+      </c>
+      <c r="O11" s="44">
         <v>45136.719444444447</v>
       </c>
       <c r="P11" s="4">
@@ -3002,7 +2968,7 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="14">
         <v>45136.656944444447</v>
@@ -3020,25 +2986,25 @@
         <v>31.97</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="H12" s="47">
+        <v>136</v>
+      </c>
+      <c r="H12" s="40">
         <f t="shared" si="0"/>
         <v>250.602</v>
       </c>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="50">
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="42">
         <v>227.82</v>
       </c>
-      <c r="M12" s="72">
+      <c r="M12" s="37">
         <f>AVERAGE(F40:F44)</f>
         <v>49.308000000000007</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="O12" s="52">
+        <v>82</v>
+      </c>
+      <c r="O12" s="44">
         <v>45136.729861111111</v>
       </c>
       <c r="P12" s="4">
@@ -3046,12 +3012,12 @@
         <v>50.82</v>
       </c>
       <c r="Q12" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="14">
         <v>45136.667361111111</v>
@@ -3069,16 +3035,16 @@
         <v>48.64</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="M13" s="72">
+        <v>137</v>
+      </c>
+      <c r="M13" s="37">
         <f>AVERAGE(F45:F49)</f>
         <v>35.209999999999994</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="O13" s="52">
+        <v>88</v>
+      </c>
+      <c r="O13" s="44">
         <v>45136.740277777775</v>
       </c>
       <c r="P13" s="4">
@@ -3091,7 +3057,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B14" s="14">
         <v>45136.667361111111</v>
@@ -3109,16 +3075,16 @@
         <v>48.11</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="72">
+        <v>140</v>
+      </c>
+      <c r="M14" s="37">
         <f>AVERAGE(F50:F53)</f>
         <v>51.822499999999998</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="52">
+        <v>93</v>
+      </c>
+      <c r="O14" s="44">
         <v>45136.750694444447</v>
       </c>
       <c r="P14" s="4">
@@ -3126,12 +3092,12 @@
         <v>48.344999999999999</v>
       </c>
       <c r="Q14" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" s="14">
         <v>45136.667361111111</v>
@@ -3149,16 +3115,16 @@
         <v>46.49</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="M15" s="72">
+        <v>141</v>
+      </c>
+      <c r="M15" s="37">
         <f>AVERAGE(F54:F58)</f>
         <v>52.998000000000005</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="O15" s="52">
+        <v>118</v>
+      </c>
+      <c r="O15" s="44">
         <v>45136.761111111111</v>
       </c>
       <c r="P15" s="4">
@@ -3166,12 +3132,12 @@
         <v>74.881999999999991</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="14">
         <v>45136.667361111111</v>
@@ -3189,16 +3155,16 @@
         <v>48.06</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="M16" s="72">
+        <v>139</v>
+      </c>
+      <c r="M16" s="37">
         <f>AVERAGE(F59:F63)</f>
         <v>74.873999999999995</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="O16" s="52">
+        <v>119</v>
+      </c>
+      <c r="O16" s="44">
         <v>45136.771527777775</v>
       </c>
       <c r="P16" s="4">
@@ -3211,7 +3177,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="14">
         <v>45136.667361111111</v>
@@ -3229,16 +3195,16 @@
         <v>48.41</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="M17" s="72">
+        <v>138</v>
+      </c>
+      <c r="M17" s="37">
         <f>AVERAGE(F64:F68)</f>
         <v>67.72999999999999</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="O17" s="52">
+        <v>120</v>
+      </c>
+      <c r="O17" s="44">
         <v>45136.781944444447</v>
       </c>
       <c r="P17" s="4">
@@ -3246,12 +3212,12 @@
         <v>91.213999999999999</v>
       </c>
       <c r="Q17" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="14">
         <v>45136.677777777775</v>
@@ -3269,16 +3235,16 @@
         <v>38.07</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="M18" s="72">
+        <v>142</v>
+      </c>
+      <c r="M18" s="37">
         <f>AVERAGE(F69:F73)</f>
         <v>72.894000000000005</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="O18" s="52">
+        <v>121</v>
+      </c>
+      <c r="O18" s="44">
         <v>45136.792361111111</v>
       </c>
       <c r="P18" s="4">
@@ -3286,12 +3252,12 @@
         <v>74.50800000000001</v>
       </c>
       <c r="Q18" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="14">
         <v>45136.677777777775</v>
@@ -3309,16 +3275,16 @@
         <v>36.4</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="M19" s="72">
+        <v>143</v>
+      </c>
+      <c r="M19" s="37">
         <f>AVERAGE(F74:F78)</f>
         <v>105.13399999999999</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="O19" s="52">
+        <v>101</v>
+      </c>
+      <c r="O19" s="44">
         <v>45136.802777777775</v>
       </c>
       <c r="P19" s="4">
@@ -3326,12 +3292,12 @@
         <v>81.948000000000008</v>
       </c>
       <c r="Q19" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="21">
         <v>45136.677777777775</v>
@@ -3349,17 +3315,17 @@
         <v>38.590000000000003</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H20" s="12"/>
-      <c r="M20" s="72">
+      <c r="M20" s="37">
         <f>AVERAGE(F79:F83)</f>
         <v>48.81600000000001</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="O20" s="52">
+        <v>106</v>
+      </c>
+      <c r="O20" s="44">
         <v>45136.813194444447</v>
       </c>
       <c r="P20" s="4">
@@ -3367,12 +3333,12 @@
         <v>52.010000000000005</v>
       </c>
       <c r="Q20" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="14">
         <v>45136.688194444447</v>
@@ -3390,29 +3356,29 @@
         <v>39.409999999999997</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="M21" s="72">
+        <v>145</v>
+      </c>
+      <c r="M21" s="37">
         <f>AVERAGE(F84:F89)</f>
         <v>65.501666666666665</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="O21" s="52">
+        <v>107</v>
+      </c>
+      <c r="O21" s="44">
         <v>45136.823611111111</v>
       </c>
-      <c r="P21" s="53">
+      <c r="P21" s="45">
         <f>AVERAGE(E84:E89)</f>
         <v>52.246666666666663</v>
       </c>
       <c r="Q21" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="14">
         <v>45136.688194444447</v>
@@ -3430,16 +3396,16 @@
         <v>41.41</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="M22" s="72">
+        <v>146</v>
+      </c>
+      <c r="M22" s="37">
         <f>AVERAGE(F90:F94)</f>
         <v>59.455999999999996</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="O22" s="52">
+        <v>108</v>
+      </c>
+      <c r="O22" s="44">
         <v>45136.834027777775</v>
       </c>
       <c r="P22" s="4">
@@ -3447,12 +3413,12 @@
         <v>48.755000000000003</v>
       </c>
       <c r="Q22" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" s="14">
         <v>45136.688194444447</v>
@@ -3470,16 +3436,16 @@
         <v>41.67</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="M23" s="72">
+        <v>147</v>
+      </c>
+      <c r="M23" s="37">
         <f>AVERAGE(F96:F99)</f>
         <v>60.007500000000007</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="O23" s="52">
+        <v>109</v>
+      </c>
+      <c r="O23" s="44">
         <v>45136.844444444447</v>
       </c>
       <c r="P23" s="4">
@@ -3487,12 +3453,12 @@
         <v>48.024000000000001</v>
       </c>
       <c r="Q23" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="14">
         <v>45136.698611111111</v>
@@ -3510,16 +3476,16 @@
         <v>57.26</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="M24" s="72">
+        <v>125</v>
+      </c>
+      <c r="M24" s="37">
         <f>AVERAGE(F101:F105)</f>
         <v>68.61</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="O24" s="52">
+        <v>110</v>
+      </c>
+      <c r="O24" s="44">
         <v>45136.854861111111</v>
       </c>
       <c r="P24" s="4">
@@ -3527,12 +3493,12 @@
         <v>44.088000000000001</v>
       </c>
       <c r="Q24" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="14">
         <v>45136.698611111111</v>
@@ -3550,25 +3516,25 @@
         <v>60.73</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="M25" s="72"/>
+        <v>126</v>
+      </c>
+      <c r="M25" s="37"/>
       <c r="N25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="O25" s="52">
+        <v>111</v>
+      </c>
+      <c r="O25" s="44">
         <v>45136.865277777775</v>
       </c>
       <c r="P25" s="4">
         <v>0</v>
       </c>
       <c r="Q25" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="14">
         <v>45136.698611111111</v>
@@ -3586,29 +3552,29 @@
         <v>62.87</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="M26" s="72">
+        <v>127</v>
+      </c>
+      <c r="M26" s="37">
         <f>AVERAGE(F107:F108,F110)</f>
         <v>76.40666666666668</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="O26" s="52">
+        <v>112</v>
+      </c>
+      <c r="O26" s="44">
         <v>45136.875694444447</v>
       </c>
-      <c r="P26" s="53">
+      <c r="P26" s="45">
         <f>AVERAGE(E110,E107:E108)</f>
         <v>37.736666666666665</v>
       </c>
       <c r="Q26" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="14">
         <v>45136.698611111111</v>
@@ -3626,12 +3592,12 @@
         <v>65.349999999999994</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="14">
         <v>45136.698611111111</v>
@@ -3649,12 +3615,12 @@
         <v>70.77</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" s="14">
         <v>45136.709027777775</v>
@@ -3672,12 +3638,12 @@
         <v>50.04</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" s="14">
         <v>45136.709027777775</v>
@@ -3695,12 +3661,12 @@
         <v>47.08</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="14">
         <v>45136.709027777775</v>
@@ -3718,12 +3684,12 @@
         <v>49.79</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="14">
         <v>45136.709027777775</v>
@@ -3741,12 +3707,12 @@
         <v>59.4</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" s="14">
         <v>45136.709027777775</v>
@@ -3764,12 +3730,12 @@
         <v>61.3</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="14">
         <v>45136.709027777775</v>
@@ -3787,12 +3753,12 @@
         <v>54.48</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" s="14">
         <v>45136.719444444447</v>
@@ -3810,12 +3776,12 @@
         <v>48.33</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36" s="14">
         <v>45136.719444444447</v>
@@ -3833,12 +3799,12 @@
         <v>47.29</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" s="14">
         <v>45136.719444444447</v>
@@ -3856,12 +3822,12 @@
         <v>52.43</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" s="14">
         <v>45136.719444444447</v>
@@ -3879,12 +3845,12 @@
         <v>52.82</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" s="14">
         <v>45136.719444444447</v>
@@ -3902,12 +3868,12 @@
         <v>52.94</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B40" s="14">
         <v>45136.729861111111</v>
@@ -3925,12 +3891,12 @@
         <v>46.84</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="14">
         <v>45136.729861111111</v>
@@ -3948,12 +3914,12 @@
         <v>57.06</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B42" s="14">
         <v>45136.729861111111</v>
@@ -3971,12 +3937,12 @@
         <v>46.39</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" s="14">
         <v>45136.729861111111</v>
@@ -3994,12 +3960,12 @@
         <v>47.69</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="14">
         <v>45136.729861111111</v>
@@ -4017,12 +3983,12 @@
         <v>48.56</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B45" s="14">
         <v>45136.740277777775</v>
@@ -4040,12 +4006,12 @@
         <v>33.78</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" s="14">
         <v>45136.740277777775</v>
@@ -4063,12 +4029,12 @@
         <v>34.729999999999997</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B47" s="14">
         <v>45136.740277777775</v>
@@ -4086,12 +4052,12 @@
         <v>37.54</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B48" s="14">
         <v>45136.740277777775</v>
@@ -4109,12 +4075,12 @@
         <v>35.24</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B49" s="14">
         <v>45136.740277777775</v>
@@ -4132,12 +4098,12 @@
         <v>34.76</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" s="14">
         <v>45136.750694444447</v>
@@ -4155,12 +4121,12 @@
         <v>48.15</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B51" s="14">
         <v>45136.750694444447</v>
@@ -4178,12 +4144,12 @@
         <v>50.42</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B52" s="14">
         <v>45136.750694444447</v>
@@ -4201,12 +4167,12 @@
         <v>50.96</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53" s="14">
         <v>45136.750694444447</v>
@@ -4224,12 +4190,12 @@
         <v>57.76</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B54" s="14">
         <v>45136.761111111111</v>
@@ -4247,12 +4213,12 @@
         <v>50</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B55" s="14">
         <v>45136.761111111111</v>
@@ -4270,12 +4236,12 @@
         <v>56.93</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B56" s="14">
         <v>45136.761111111111</v>
@@ -4293,12 +4259,12 @@
         <v>60.71</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B57" s="14">
         <v>45136.761111111111</v>
@@ -4316,12 +4282,12 @@
         <v>49.93</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B58" s="14">
         <v>45136.761111111111</v>
@@ -4339,12 +4305,12 @@
         <v>47.42</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B59" s="14">
         <v>45136.771527777775</v>
@@ -4362,12 +4328,12 @@
         <v>76.180000000000007</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B60" s="14">
         <v>45136.771527777775</v>
@@ -4385,12 +4351,12 @@
         <v>80.900000000000006</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B61" s="14">
         <v>45136.771527777775</v>
@@ -4408,12 +4374,12 @@
         <v>75.09</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B62" s="14">
         <v>45136.771527777775</v>
@@ -4431,12 +4397,12 @@
         <v>65.23</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B63" s="14">
         <v>45136.771527777775</v>
@@ -4454,12 +4420,12 @@
         <v>76.97</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B64" s="14">
         <v>45136.781944444447</v>
@@ -4477,12 +4443,12 @@
         <v>72.17</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B65" s="14">
         <v>45136.781944444447</v>
@@ -4500,12 +4466,12 @@
         <v>73.53</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B66" s="14">
         <v>45136.781944444447</v>
@@ -4523,12 +4489,12 @@
         <v>66.12</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B67" s="14">
         <v>45136.781944444447</v>
@@ -4546,12 +4512,12 @@
         <v>73.08</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B68" s="14">
         <v>45136.781944444447</v>
@@ -4569,12 +4535,12 @@
         <v>53.75</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B69" s="14">
         <v>45136.792361111111</v>
@@ -4592,12 +4558,12 @@
         <v>76.03</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B70" s="14">
         <v>45136.792361111111</v>
@@ -4615,12 +4581,12 @@
         <v>73.95</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B71" s="14">
         <v>45136.792361111111</v>
@@ -4638,12 +4604,12 @@
         <v>75.400000000000006</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B72" s="14">
         <v>45136.792361111111</v>
@@ -4661,12 +4627,12 @@
         <v>68.62</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B73" s="14">
         <v>45136.792361111111</v>
@@ -4684,12 +4650,12 @@
         <v>70.47</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B74" s="14">
         <v>45136.802777777775</v>
@@ -4707,12 +4673,12 @@
         <v>108.27</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B75" s="14">
         <v>45136.802777777775</v>
@@ -4730,12 +4696,12 @@
         <v>93.42</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B76" s="14">
         <v>45136.802777777775</v>
@@ -4753,12 +4719,12 @@
         <v>105.28</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B77" s="14">
         <v>45136.802777777775</v>
@@ -4776,12 +4742,12 @@
         <v>111.53</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B78" s="14">
         <v>45136.802777777775</v>
@@ -4799,12 +4765,12 @@
         <v>107.17</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B79" s="14">
         <v>45136.813194444447</v>
@@ -4822,12 +4788,12 @@
         <v>48.99</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B80" s="14">
         <v>45136.813194444447</v>
@@ -4845,12 +4811,12 @@
         <v>50.91</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B81" s="14">
         <v>45136.813194444447</v>
@@ -4868,12 +4834,12 @@
         <v>50.39</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B82" s="14">
         <v>45136.813194444447</v>
@@ -4891,12 +4857,12 @@
         <v>47.67</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B83" s="14">
         <v>45136.813194444447</v>
@@ -4914,12 +4880,12 @@
         <v>46.12</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B84" s="14">
         <v>45136.823611111111</v>
@@ -4937,12 +4903,12 @@
         <v>68.66</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B85" s="14">
         <v>45136.823611111111</v>
@@ -4960,12 +4926,12 @@
         <v>71.33</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B86" s="14">
         <v>45136.823611111111</v>
@@ -4983,12 +4949,12 @@
         <v>78.010000000000005</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B87" s="14">
         <v>45136.823611111111</v>
@@ -5006,12 +4972,12 @@
         <v>60.5</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B88" s="14">
         <v>45136.823611111111</v>
@@ -5029,12 +4995,12 @@
         <v>56</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B89" s="14">
         <v>45136.823611111111</v>
@@ -5052,12 +5018,12 @@
         <v>58.51</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B90" s="14">
         <v>45136.834027777775</v>
@@ -5075,12 +5041,12 @@
         <v>63.08</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B91" s="14">
         <v>45136.834027777775</v>
@@ -5098,12 +5064,12 @@
         <v>61.82</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B92" s="14">
         <v>45136.834027777775</v>
@@ -5121,12 +5087,12 @@
         <v>61.69</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B93" s="14">
         <v>45136.834027777775</v>
@@ -5144,12 +5110,12 @@
         <v>53.82</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B94" s="14">
         <v>45136.834027777775</v>
@@ -5167,12 +5133,12 @@
         <v>56.87</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B95" s="14">
         <v>45136.834027777775</v>
@@ -5190,12 +5156,12 @@
         <v>54.2</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" s="14">
         <v>45136.844444444447</v>
@@ -5213,12 +5179,12 @@
         <v>60.2</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B97" s="14">
         <v>45136.844444444447</v>
@@ -5236,12 +5202,12 @@
         <v>60.91</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B98" s="14">
         <v>45136.844444444447</v>
@@ -5259,12 +5225,12 @@
         <v>64.25</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B99" s="14">
         <v>45136.844444444447</v>
@@ -5282,12 +5248,12 @@
         <v>54.67</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B100" s="14">
         <v>45136.844444444447</v>
@@ -5305,12 +5271,12 @@
         <v>54.54</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" s="14">
         <v>45136.854861111111</v>
@@ -5328,12 +5294,12 @@
         <v>70.150000000000006</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B102" s="14">
         <v>45136.854861111111</v>
@@ -5351,12 +5317,12 @@
         <v>71.55</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" s="14">
         <v>45136.854861111111</v>
@@ -5374,12 +5340,12 @@
         <v>78</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="104" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="14">
         <v>45136.854861111111</v>
@@ -5397,12 +5363,12 @@
         <v>61.66</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="14">
         <v>45136.854861111111</v>
@@ -5420,25 +5386,25 @@
         <v>61.69</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M105" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="N105" s="78" t="s">
-        <v>82</v>
-      </c>
-      <c r="O105" s="79"/>
-      <c r="P105" s="63" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q105" s="31" t="s">
-        <v>496</v>
+        <v>2</v>
+      </c>
+      <c r="N105" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="O105" s="68"/>
+      <c r="P105" s="55" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q105" s="30" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B106" s="14">
         <v>45136.865277777775</v>
@@ -5447,28 +5413,28 @@
         <v>0</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E106" s="4">
         <v>0</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M106" s="12">
         <f>AVERAGE(F112:F116)</f>
         <v>34.543999999999997</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O106" s="14">
         <v>45136.629861111112</v>
       </c>
-      <c r="P106" s="53">
+      <c r="P106" s="45">
         <f>AVERAGE(H113:H116)</f>
         <v>223.61406716417912</v>
       </c>
@@ -5478,7 +5444,7 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B107" s="14">
         <v>45136.875694444447</v>
@@ -5496,19 +5462,19 @@
         <v>77.37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M107" s="12">
         <f>AVERAGE(F118:F122)</f>
         <v>28.583999999999996</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O107" s="14">
         <v>45136.640277777777</v>
       </c>
-      <c r="P107" s="53">
+      <c r="P107" s="45">
         <f>AVERAGE(H118:H122,E117)</f>
         <v>200.69044776119404</v>
       </c>
@@ -5518,7 +5484,7 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B108" s="14">
         <v>45136.875694444447</v>
@@ -5536,19 +5502,19 @@
         <v>76.36</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M108" s="12">
         <f>AVERAGE(F123:F126)</f>
         <v>39.422499999999999</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O108" s="14">
         <v>45136.650694444441</v>
       </c>
-      <c r="P108" s="53">
+      <c r="P108" s="45">
         <f>AVERAGE(E123,E124,E125,H127)</f>
         <v>231.91373134328356</v>
       </c>
@@ -5558,7 +5524,7 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" s="14">
         <v>45136.875694444447</v>
@@ -5573,17 +5539,17 @@
         <v>0</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M109" s="12">
         <f>AVERAGE(F127:F130)</f>
         <v>50.475000000000001</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O109" s="14">
         <v>45136.661111111112</v>
@@ -5598,7 +5564,7 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B110" s="14">
         <v>45136.875694444447</v>
@@ -5616,14 +5582,14 @@
         <v>75.489999999999995</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M110" s="12">
         <f>AVERAGE(F131:F135)</f>
         <v>44.345999999999997</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O110" s="14">
         <v>45136.671527777777</v>
@@ -5638,7 +5604,7 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B111" s="14">
         <v>45136.875694444447</v>
@@ -5653,15 +5619,15 @@
         <v>0</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B112" s="14">
         <v>45136.629861111112</v>
@@ -5679,27 +5645,27 @@
         <v>32.47</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="H112" s="60" t="s">
-        <v>231</v>
+        <v>228</v>
+      </c>
+      <c r="H112" s="52" t="s">
+        <v>230</v>
       </c>
       <c r="I112" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J112" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="J112" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="K112" s="46" t="s">
-        <v>491</v>
+      <c r="K112" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="L112" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B113" s="14">
         <v>45136.629861111112</v>
@@ -5717,9 +5683,9 @@
         <v>45.57</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="H113" s="61">
+        <v>229</v>
+      </c>
+      <c r="H113" s="53">
         <f>K113/(1-($J$113/$I$113))</f>
         <v>220.37910447761195</v>
       </c>
@@ -5735,7 +5701,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B114" s="14">
         <v>45136.629861111112</v>
@@ -5753,21 +5719,21 @@
         <v>32.17</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="H114" s="61">
+        <v>231</v>
+      </c>
+      <c r="H114" s="53">
         <f>K114/(1-($J$113/$I$113))</f>
         <v>224.91940298507467</v>
       </c>
-      <c r="I114" s="44"/>
-      <c r="J114" s="44"/>
+      <c r="I114" s="38"/>
+      <c r="J114" s="38"/>
       <c r="K114" s="5">
         <v>128.80000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B115" s="14">
         <v>45136.629861111112</v>
@@ -5785,21 +5751,21 @@
         <v>31.15</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="H115" s="61">
+        <v>232</v>
+      </c>
+      <c r="H115" s="53">
         <f t="shared" ref="H115" si="1">K115/(1-($J$113/$I$113))</f>
         <v>222.82388059701492</v>
       </c>
-      <c r="I115" s="44"/>
-      <c r="J115" s="44"/>
+      <c r="I115" s="38"/>
+      <c r="J115" s="38"/>
       <c r="K115" s="5">
         <v>127.6</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B116" s="14">
         <v>45136.629861111112</v>
@@ -5817,21 +5783,21 @@
         <v>31.36</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="H116" s="62">
+        <v>233</v>
+      </c>
+      <c r="H116" s="54">
         <f>K116/(1-($J$113/$I$113))</f>
         <v>226.33388059701497</v>
       </c>
-      <c r="I116" s="51"/>
-      <c r="J116" s="51"/>
-      <c r="K116" s="50">
+      <c r="I116" s="43"/>
+      <c r="J116" s="43"/>
+      <c r="K116" s="42">
         <v>129.61000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B117" s="14">
         <v>45136.640277777777</v>
@@ -5849,27 +5815,27 @@
         <v>40.9</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="H117" s="60" t="s">
-        <v>199</v>
+        <v>195</v>
+      </c>
+      <c r="H117" s="52" t="s">
+        <v>198</v>
       </c>
       <c r="I117" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="K117" s="46" t="s">
-        <v>495</v>
+      <c r="K117" s="2" t="s">
+        <v>494</v>
       </c>
       <c r="L117" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B118" s="14">
         <v>45136.640277777777</v>
@@ -5887,9 +5853,9 @@
         <v>23.42</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="H118" s="61">
+        <v>196</v>
+      </c>
+      <c r="H118" s="53">
         <f>K118/(1-($J$118/$I$118))</f>
         <v>155.10358208955225</v>
       </c>
@@ -5905,7 +5871,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B119" s="14">
         <v>45136.640277777777</v>
@@ -5923,21 +5889,21 @@
         <v>30.13</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="H119" s="61">
+        <v>201</v>
+      </c>
+      <c r="H119" s="53">
         <f t="shared" ref="H119:H122" si="2">K119/(1-($J$118/$I$118))</f>
         <v>183.72492537313434</v>
       </c>
-      <c r="I119" s="44"/>
-      <c r="J119" s="44"/>
+      <c r="I119" s="38"/>
+      <c r="J119" s="38"/>
       <c r="K119" s="5">
         <v>105.21</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B120" s="14">
         <v>45136.640277777777</v>
@@ -5955,21 +5921,21 @@
         <v>31.7</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="H120" s="61">
+        <v>199</v>
+      </c>
+      <c r="H120" s="53">
         <f t="shared" si="2"/>
         <v>215.71656716417911</v>
       </c>
-      <c r="I120" s="44"/>
-      <c r="J120" s="44"/>
+      <c r="I120" s="38"/>
+      <c r="J120" s="38"/>
       <c r="K120" s="5">
         <v>123.53</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B121" s="14">
         <v>45136.640277777777</v>
@@ -5987,21 +5953,21 @@
         <v>29.32</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="H121" s="61">
+        <v>200</v>
+      </c>
+      <c r="H121" s="53">
         <f t="shared" si="2"/>
         <v>204.62776119402989</v>
       </c>
-      <c r="I121" s="44"/>
-      <c r="J121" s="44"/>
+      <c r="I121" s="38"/>
+      <c r="J121" s="38"/>
       <c r="K121" s="5">
         <v>117.18</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B122" s="14">
         <v>45136.640277777777</v>
@@ -6019,21 +5985,21 @@
         <v>28.35</v>
       </c>
       <c r="G122" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="H122" s="62">
+        <v>202</v>
+      </c>
+      <c r="H122" s="54">
         <f t="shared" si="2"/>
         <v>195.45985074626867</v>
       </c>
-      <c r="I122" s="51"/>
-      <c r="J122" s="51"/>
-      <c r="K122" s="50">
+      <c r="I122" s="43"/>
+      <c r="J122" s="43"/>
+      <c r="K122" s="42">
         <v>111.93</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B123" s="14">
         <v>45136.650694444441</v>
@@ -6051,12 +6017,12 @@
         <v>44.5</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B124" s="14">
         <v>45136.650694444441</v>
@@ -6074,12 +6040,12 @@
         <v>44.41</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B125" s="14">
         <v>45136.650694444441</v>
@@ -6097,12 +6063,12 @@
         <v>42.41</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B126" s="14">
         <v>45136.650694444441</v>
@@ -6120,24 +6086,24 @@
         <v>26.37</v>
       </c>
       <c r="G126" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="H126" s="58" t="s">
         <v>243</v>
       </c>
+      <c r="H126" s="50" t="s">
+        <v>242</v>
+      </c>
       <c r="I126" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="J126" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="J126" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="K126" s="28" t="s">
-        <v>495</v>
+      <c r="K126" s="4" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B127" s="14">
         <v>45136.661111111112</v>
@@ -6155,9 +6121,9 @@
         <v>49.41</v>
       </c>
       <c r="G127" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="H127" s="59">
+        <v>244</v>
+      </c>
+      <c r="H127" s="51">
         <f>K127/(1-($J$127/$I$127))</f>
         <v>193.08492537313433</v>
       </c>
@@ -6173,7 +6139,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B128" s="14">
         <v>45136.661111111112</v>
@@ -6191,12 +6157,12 @@
         <v>51.85</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B129" s="14">
         <v>45136.661111111112</v>
@@ -6214,12 +6180,12 @@
         <v>50.11</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B130" s="14">
         <v>45136.661111111112</v>
@@ -6237,12 +6203,12 @@
         <v>50.53</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B131" s="14">
         <v>45136.671527777777</v>
@@ -6260,12 +6226,12 @@
         <v>39.94</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B132" s="14">
         <v>45136.671527777777</v>
@@ -6283,12 +6249,12 @@
         <v>44.37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B133" s="14">
         <v>45136.671527777777</v>
@@ -6306,12 +6272,12 @@
         <v>45.85</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B134" s="14">
         <v>45136.671527777777</v>
@@ -6329,12 +6295,12 @@
         <v>43.16</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B135" s="14">
         <v>45136.671527777777</v>
@@ -6352,7 +6318,7 @@
         <v>48.41</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -6384,42 +6350,42 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="75"/>
+      <c r="A2" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="64"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="75"/>
-      <c r="K2" s="43" t="s">
+      <c r="I2" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="M2" s="62" t="s">
         <v>2</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="M2" s="73" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="11">
         <v>45151.78125</v>
@@ -6437,12 +6403,12 @@
         <v>55.86</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="65">
+        <v>16</v>
+      </c>
+      <c r="J3" s="57">
         <v>45151.78125</v>
       </c>
       <c r="K3" s="1">
@@ -6459,7 +6425,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="9">
         <v>45151.78125</v>
@@ -6477,10 +6443,10 @@
         <v>51.63</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J4" s="9">
         <v>45151.790277777778</v>
@@ -6499,7 +6465,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="9">
         <v>45151.78125</v>
@@ -6517,10 +6483,10 @@
         <v>52.12</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" s="9">
         <v>45151.793055555558</v>
@@ -6539,7 +6505,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="9">
         <v>45151.78125</v>
@@ -6557,10 +6523,10 @@
         <v>52.09</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" s="9">
         <v>45151.798611111109</v>
@@ -6579,7 +6545,7 @@
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="9">
         <v>45151.790277777778</v>
@@ -6597,15 +6563,15 @@
         <v>45.86</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="64">
+        <v>25</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="56">
         <v>45151.876388888886</v>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="41">
         <f>AVERAGE(E21:E24)</f>
         <v>56.15</v>
       </c>
@@ -6619,7 +6585,7 @@
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="9">
         <v>45151.790277777778</v>
@@ -6637,13 +6603,13 @@
         <v>42.8</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="9">
         <v>45151.790277777778</v>
@@ -6661,25 +6627,25 @@
         <v>44.97</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="80"/>
-      <c r="K9" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="69"/>
+      <c r="K9" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="M9" s="62" t="s">
         <v>2</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="M9" s="73" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="9">
         <v>45151.790277777778</v>
@@ -6697,12 +6663,12 @@
         <v>48.17</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="66">
+        <v>28</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="58">
         <v>45151.78125</v>
       </c>
       <c r="K10" s="1">
@@ -6719,7 +6685,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="9">
         <v>45151.790277777778</v>
@@ -6737,10 +6703,10 @@
         <v>48.14</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J11" s="9">
         <v>45151.791666666664</v>
@@ -6759,7 +6725,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="9">
         <v>45151.793055555558</v>
@@ -6777,10 +6743,10 @@
         <v>49.25</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J12" s="9">
         <v>45151.802083333336</v>
@@ -6799,7 +6765,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="9">
         <v>45151.793055555558</v>
@@ -6817,15 +6783,15 @@
         <v>52.07</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J13" s="9">
         <v>45151.8125</v>
       </c>
-      <c r="K13" s="30">
+      <c r="K13" s="29">
         <f>AVERAGE(E40:E42)</f>
         <v>67.606666666666669</v>
       </c>
@@ -6839,7 +6805,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="9">
         <v>45151.793055555558</v>
@@ -6857,10 +6823,10 @@
         <v>53.99</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14" s="9">
         <v>45151.822916666664</v>
@@ -6879,7 +6845,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="9">
         <v>45151.793055555558</v>
@@ -6897,10 +6863,10 @@
         <v>56.19</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" s="9">
         <v>45151.833333333336</v>
@@ -6919,7 +6885,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="9">
         <v>45151.793055555558</v>
@@ -6937,10 +6903,10 @@
         <v>52.14</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J16" s="9">
         <v>45151.84375</v>
@@ -6959,7 +6925,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="9">
         <v>45151.798611111109</v>
@@ -6977,10 +6943,10 @@
         <v>49.62</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J17" s="9">
         <v>45151.854166666664</v>
@@ -6999,7 +6965,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="9">
         <v>45151.798611111109</v>
@@ -7017,10 +6983,10 @@
         <v>49.82</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J18" s="9">
         <v>45151.864583333336</v>
@@ -7039,7 +7005,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="9">
         <v>45151.798611111109</v>
@@ -7057,10 +7023,10 @@
         <v>49.79</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J19" s="9">
         <v>45151.875</v>
@@ -7079,7 +7045,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="9">
         <v>45151.798611111109</v>
@@ -7097,10 +7063,10 @@
         <v>50</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J20" s="9">
         <v>45151.885416666664</v>
@@ -7119,7 +7085,7 @@
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="9">
         <v>45151.876388888886</v>
@@ -7137,15 +7103,15 @@
         <v>43.15</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="64">
+        <v>39</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="J21" s="56">
         <v>45151.895833333336</v>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="41">
         <f>AVERAGE(E63:E67)</f>
         <v>50.773999999999994</v>
       </c>
@@ -7159,7 +7125,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="9">
         <v>45151.876388888886</v>
@@ -7177,12 +7143,12 @@
         <v>44.56</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="9">
         <v>45151.876388888886</v>
@@ -7200,12 +7166,12 @@
         <v>45.37</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="9">
         <v>45151.876388888886</v>
@@ -7223,12 +7189,12 @@
         <v>45.89</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B26" s="9">
         <v>45151.78125</v>
@@ -7246,12 +7212,12 @@
         <v>88.64</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="9">
         <v>45151.78125</v>
@@ -7269,12 +7235,12 @@
         <v>89.4</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="9">
         <v>45151.78125</v>
@@ -7292,12 +7258,12 @@
         <v>88.04</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="9">
         <v>45151.78125</v>
@@ -7315,12 +7281,12 @@
         <v>87.48</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="9">
         <v>45151.78125</v>
@@ -7338,12 +7304,12 @@
         <v>94.11</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="9">
         <v>45151.791666666664</v>
@@ -7361,12 +7327,12 @@
         <v>47.35</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" s="9">
         <v>45151.791666666664</v>
@@ -7384,12 +7350,12 @@
         <v>46.72</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="9">
         <v>45151.791666666664</v>
@@ -7407,12 +7373,12 @@
         <v>47.27</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="9">
         <v>45151.791666666664</v>
@@ -7430,12 +7396,12 @@
         <v>43.23</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="9">
         <v>45151.791666666664</v>
@@ -7453,12 +7419,12 @@
         <v>45.72</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" s="9">
         <v>45151.802083333336</v>
@@ -7476,12 +7442,12 @@
         <v>54.09</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="9">
         <v>45151.802083333336</v>
@@ -7499,12 +7465,12 @@
         <v>50.22</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" s="9">
         <v>45151.802083333336</v>
@@ -7522,12 +7488,12 @@
         <v>48.5</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B39" s="9">
         <v>45151.802083333336</v>
@@ -7545,12 +7511,12 @@
         <v>48.8</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="9">
         <v>45151.8125</v>
@@ -7568,12 +7534,12 @@
         <v>51.55</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="9">
         <v>45151.8125</v>
@@ -7591,12 +7557,12 @@
         <v>50.58</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42" s="9">
         <v>45151.8125</v>
@@ -7614,12 +7580,12 @@
         <v>53.67</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" s="9">
         <v>45151.8125</v>
@@ -7633,12 +7599,12 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="9">
         <v>45151.822916666664</v>
@@ -7656,12 +7622,12 @@
         <v>59.06</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" s="9">
         <v>45151.833333333336</v>
@@ -7679,12 +7645,12 @@
         <v>56.53</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" s="9">
         <v>45151.84375</v>
@@ -7702,12 +7668,12 @@
         <v>78.86</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" s="9">
         <v>45151.854166666664</v>
@@ -7725,12 +7691,12 @@
         <v>82.1</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="9">
         <v>45151.864583333336</v>
@@ -7748,12 +7714,12 @@
         <v>53.95</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="9">
         <v>45151.864583333336</v>
@@ -7771,12 +7737,12 @@
         <v>52.02</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B50" s="9">
         <v>45151.864583333336</v>
@@ -7794,12 +7760,12 @@
         <v>53.69</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="9">
         <v>45151.864583333336</v>
@@ -7817,12 +7783,12 @@
         <v>49.25</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="9">
         <v>45151.864583333336</v>
@@ -7840,12 +7806,12 @@
         <v>50.21</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B53" s="9">
         <v>45151.875</v>
@@ -7863,12 +7829,12 @@
         <v>45.93</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B54" s="9">
         <v>45151.875</v>
@@ -7886,12 +7852,12 @@
         <v>55.84</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B55" s="9">
         <v>45151.875</v>
@@ -7909,12 +7875,12 @@
         <v>48.05</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B56" s="9">
         <v>45151.875</v>
@@ -7932,12 +7898,12 @@
         <v>50.31</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B57" s="9">
         <v>45151.875</v>
@@ -7955,12 +7921,12 @@
         <v>51.72</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B58" s="9">
         <v>45151.885416666664</v>
@@ -7978,12 +7944,12 @@
         <v>46.85</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B59" s="9">
         <v>45151.885416666664</v>
@@ -8001,12 +7967,12 @@
         <v>56.08</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" s="9">
         <v>45151.885416666664</v>
@@ -8024,12 +7990,12 @@
         <v>48.43</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B61" s="9">
         <v>45151.885416666664</v>
@@ -8047,12 +8013,12 @@
         <v>50.48</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B62" s="9">
         <v>45151.885416666664</v>
@@ -8070,12 +8036,12 @@
         <v>50.92</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B63" s="9">
         <v>45151.895833333336</v>
@@ -8093,12 +8059,12 @@
         <v>51.39</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B64" s="9">
         <v>45151.895833333336</v>
@@ -8116,12 +8082,12 @@
         <v>52.07</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B65" s="9">
         <v>45151.895833333336</v>
@@ -8139,12 +8105,12 @@
         <v>57.09</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B66" s="9">
         <v>45151.895833333336</v>
@@ -8162,12 +8128,12 @@
         <v>59.07</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B67" s="9">
         <v>45151.895833333336</v>
@@ -8185,7 +8151,7 @@
         <v>56.54</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -8218,41 +8184,41 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
-        <v>498</v>
-      </c>
-      <c r="B2" s="75"/>
+      <c r="A2" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" s="64"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>4</v>
-      </c>
       <c r="I2" s="23" t="s">
-        <v>498</v>
-      </c>
-      <c r="J2" s="69" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="43" t="s">
+        <v>497</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>2</v>
       </c>
+      <c r="K2" s="49" t="s">
+        <v>493</v>
+      </c>
       <c r="L2" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="1">
@@ -8268,12 +8234,12 @@
         <v>62.61</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="30">
+        <v>43</v>
+      </c>
+      <c r="J3" s="29">
         <f>AVERAGE(F3:F7)</f>
         <v>63.429999999999993</v>
       </c>
@@ -8287,7 +8253,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="4">
@@ -8303,12 +8269,12 @@
         <v>66.959999999999994</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J4" s="30">
+        <v>73</v>
+      </c>
+      <c r="J4" s="29">
         <f>AVERAGE(F8:F12)</f>
         <v>66.166000000000011</v>
       </c>
@@ -8322,7 +8288,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="4">
@@ -8338,12 +8304,12 @@
         <v>65.45</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="30">
+        <v>49</v>
+      </c>
+      <c r="J5" s="29">
         <f>AVERAGE(F13:F17)</f>
         <v>52.120000000000005</v>
       </c>
@@ -8357,7 +8323,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="4">
@@ -8373,12 +8339,12 @@
         <v>67.540000000000006</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="30">
+        <v>54</v>
+      </c>
+      <c r="J6" s="29">
         <f>AVERAGE(F18:F22)</f>
         <v>57.696000000000005</v>
       </c>
@@ -8392,7 +8358,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="4">
@@ -8408,12 +8374,12 @@
         <v>54.59</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="30">
+        <v>58</v>
+      </c>
+      <c r="J7" s="29">
         <f>AVERAGE(F23:F27)</f>
         <v>56.001999999999995</v>
       </c>
@@ -8427,7 +8393,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="4">
@@ -8443,12 +8409,12 @@
         <v>65.86</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="30">
+        <v>60</v>
+      </c>
+      <c r="J8" s="29">
         <f>AVERAGE(F28:F32)</f>
         <v>56.870000000000005</v>
       </c>
@@ -8457,12 +8423,12 @@
         <v>87.688000000000002</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="4">
@@ -8478,12 +8444,12 @@
         <v>67.790000000000006</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="30">
+        <v>62</v>
+      </c>
+      <c r="J9" s="29">
         <f>AVERAGE(F33:F37)</f>
         <v>71.585999999999999</v>
       </c>
@@ -8492,12 +8458,12 @@
         <v>95.621999999999986</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="4">
@@ -8513,12 +8479,12 @@
         <v>64.790000000000006</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="30">
+        <v>64</v>
+      </c>
+      <c r="J10" s="29">
         <f>AVERAGE(F38:F42)</f>
         <v>55.463999999999999</v>
       </c>
@@ -8532,7 +8498,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="4">
@@ -8548,12 +8514,12 @@
         <v>66.17</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" s="30">
+        <v>66</v>
+      </c>
+      <c r="J11" s="29">
         <f>AVERAGE(F43:F48)</f>
         <v>52.926666666666655</v>
       </c>
@@ -8562,12 +8528,12 @@
         <v>77.09</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="4">
@@ -8583,12 +8549,12 @@
         <v>66.22</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" s="30">
+        <v>82</v>
+      </c>
+      <c r="J12" s="29">
         <f>AVERAGE(F49:F52)</f>
         <v>47.872500000000002</v>
       </c>
@@ -8602,7 +8568,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="4">
@@ -8618,12 +8584,12 @@
         <v>52.81</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="30">
+        <v>88</v>
+      </c>
+      <c r="J13" s="29">
         <f>AVERAGE(F53:F57)</f>
         <v>65.116</v>
       </c>
@@ -8632,12 +8598,12 @@
         <v>65.813999999999993</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="4">
@@ -8653,12 +8619,12 @@
         <v>53.69</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J14" s="30">
+        <v>93</v>
+      </c>
+      <c r="J14" s="29">
         <f>AVERAGE(F58:F59)</f>
         <v>71.525000000000006</v>
       </c>
@@ -8667,12 +8633,12 @@
         <v>79.97</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="4">
@@ -8688,12 +8654,12 @@
         <v>55</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="30"/>
+        <v>118</v>
+      </c>
+      <c r="J15" s="29"/>
       <c r="K15" s="4">
         <v>0</v>
       </c>
@@ -8703,7 +8669,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="4">
@@ -8719,12 +8685,12 @@
         <v>46.56</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="4">
@@ -8740,12 +8706,12 @@
         <v>52.54</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="9"/>
       <c r="C18" s="4">
@@ -8761,12 +8727,12 @@
         <v>53.22</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="4">
@@ -8782,12 +8748,12 @@
         <v>58.67</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="4">
@@ -8803,12 +8769,12 @@
         <v>62.73</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="4">
@@ -8824,12 +8790,12 @@
         <v>58.29</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="4">
@@ -8845,12 +8811,12 @@
         <v>55.57</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="4">
@@ -8866,12 +8832,12 @@
         <v>54.48</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="9"/>
       <c r="C24" s="4">
@@ -8887,12 +8853,12 @@
         <v>54.39</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="4">
@@ -8908,12 +8874,12 @@
         <v>54.47</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" s="9"/>
       <c r="C26" s="4">
@@ -8929,12 +8895,12 @@
         <v>57.35</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="4">
@@ -8950,12 +8916,12 @@
         <v>59.32</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="4">
@@ -8971,12 +8937,12 @@
         <v>53.16</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="4">
@@ -8992,12 +8958,12 @@
         <v>56.07</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="4">
@@ -9013,12 +8979,12 @@
         <v>57.69</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="4">
@@ -9034,12 +9000,12 @@
         <v>57.34</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" s="9"/>
       <c r="C32" s="4">
@@ -9055,12 +9021,12 @@
         <v>60.09</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="4">
@@ -9076,12 +9042,12 @@
         <v>67.540000000000006</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="4">
@@ -9097,12 +9063,12 @@
         <v>87.98</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
@@ -9118,12 +9084,12 @@
         <v>67.930000000000007</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4">
@@ -9139,12 +9105,12 @@
         <v>66.81</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
@@ -9160,12 +9126,12 @@
         <v>67.67</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
@@ -9181,12 +9147,12 @@
         <v>55.24</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
@@ -9202,12 +9168,12 @@
         <v>57.62</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
@@ -9223,12 +9189,12 @@
         <v>54.43</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
@@ -9244,12 +9210,12 @@
         <v>54.74</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
@@ -9265,12 +9231,12 @@
         <v>55.29</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
@@ -9286,12 +9252,12 @@
         <v>54.41</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
@@ -9307,12 +9273,12 @@
         <v>51.64</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
@@ -9328,12 +9294,12 @@
         <v>50.74</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
@@ -9349,12 +9315,12 @@
         <v>54.82</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
@@ -9370,12 +9336,12 @@
         <v>53.79</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
@@ -9391,12 +9357,12 @@
         <v>52.16</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
@@ -9412,12 +9378,12 @@
         <v>47.82</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
@@ -9433,12 +9399,12 @@
         <v>49.07</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
@@ -9454,12 +9420,12 @@
         <v>47.05</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
@@ -9475,12 +9441,12 @@
         <v>47.55</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
@@ -9496,12 +9462,12 @@
         <v>56.96</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
@@ -9517,12 +9483,12 @@
         <v>60.53</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
@@ -9538,12 +9504,12 @@
         <v>71.58</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
@@ -9559,12 +9525,12 @@
         <v>60.35</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
@@ -9580,12 +9546,12 @@
         <v>76.16</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
@@ -9601,12 +9567,12 @@
         <v>67.81</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
@@ -9622,7 +9588,7 @@
         <v>75.239999999999995</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -9638,53 +9604,52 @@
   <dimension ref="A1:J67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="39" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="23" style="39" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="39" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="39" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="39" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="39" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="39" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="39" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="39"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>446</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="35" t="s">
+    <row r="1" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="E1" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>429</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="G1" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="H1" s="32" t="s">
         <v>430</v>
       </c>
-      <c r="G1" s="35" t="s">
-        <v>445</v>
-      </c>
-      <c r="H1" s="35" t="s">
+      <c r="I1" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="I1" s="35" t="s">
-        <v>432</v>
-      </c>
-      <c r="J1" s="67" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="59" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
@@ -9703,21 +9668,21 @@
         <v>95.95</v>
       </c>
       <c r="G2" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="I2" s="25" t="s">
         <v>449</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>450</v>
       </c>
       <c r="J2" s="4">
         <v>490</v>
       </c>
     </row>
-    <row r="3" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
@@ -9736,21 +9701,21 @@
         <v>81.680000000000007</v>
       </c>
       <c r="G3" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="H3" s="25" t="s">
         <v>451</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="I3" s="25" t="s">
         <v>452</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>453</v>
       </c>
       <c r="J3" s="4">
         <v>491</v>
       </c>
     </row>
-    <row r="4" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>50</v>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="B4" s="4">
         <v>0</v>
@@ -9765,25 +9730,25 @@
       <c r="E4" s="4">
         <v>71.44</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="29">
         <v>71.739999999999995</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>468</v>
       </c>
       <c r="J4" s="4">
         <v>492</v>
       </c>
     </row>
-    <row r="5" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>55</v>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0</v>
@@ -9802,21 +9767,21 @@
         <v>48.46</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H5" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="I5" s="25" t="s">
         <v>469</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>470</v>
-      </c>
       <c r="J5" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>59</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -9835,21 +9800,21 @@
         <v>64.52</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="J6" s="4">
         <v>493</v>
       </c>
     </row>
-    <row r="7" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>61</v>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B7" s="4">
         <v>0</v>
@@ -9868,21 +9833,21 @@
         <v>48.46</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>474</v>
-      </c>
       <c r="J7" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>63</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -9894,28 +9859,28 @@
       <c r="D8" s="4">
         <v>46.07</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="60">
         <v>51.91</v>
       </c>
-      <c r="F8" s="71">
+      <c r="F8" s="61">
         <v>60.42</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>476</v>
       </c>
       <c r="J8" s="4">
         <v>494</v>
       </c>
     </row>
-    <row r="9" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
-        <v>65</v>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -9934,21 +9899,21 @@
         <v>41.02</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>478</v>
-      </c>
       <c r="J9" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>67</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
@@ -9961,44 +9926,43 @@
         <v>39.299999999999997</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39"/>
-    </row>
-    <row r="12" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B12" s="4">
         <v>0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <f>AVERAGE(D12:F12)</f>
         <v>63.866666666666667</v>
       </c>
@@ -10012,26 +9976,26 @@
         <v>64.959999999999994</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H12" s="25" t="s">
+        <v>478</v>
+      </c>
+      <c r="I12" s="25" t="s">
         <v>479</v>
-      </c>
-      <c r="I12" s="25" t="s">
-        <v>480</v>
       </c>
       <c r="J12" s="4">
         <v>484</v>
       </c>
     </row>
-    <row r="13" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>17</v>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <v>0</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <f t="shared" ref="C13:C17" si="1">AVERAGE(D13:F13)</f>
         <v>75.403333333333322</v>
       </c>
@@ -10045,26 +10009,26 @@
         <v>78.52</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H13" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="I13" s="25" t="s">
         <v>481</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>482</v>
       </c>
       <c r="J13" s="4">
         <v>485</v>
       </c>
     </row>
-    <row r="14" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>18</v>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <v>0</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>70.74666666666667</v>
       </c>
@@ -10078,26 +10042,26 @@
         <v>72.900000000000006</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H14" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="I14" s="25" t="s">
         <v>483</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>484</v>
       </c>
       <c r="J14" s="4">
         <v>486</v>
       </c>
     </row>
-    <row r="15" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32" t="s">
-        <v>19</v>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>61.610000000000007</v>
       </c>
@@ -10111,26 +10075,26 @@
         <v>61.13</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H15" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>486</v>
-      </c>
       <c r="J15" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
-        <v>20</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>82.603333333333339</v>
       </c>
@@ -10144,26 +10108,26 @@
         <v>85.72</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>488</v>
       </c>
       <c r="J16" s="4">
         <v>487</v>
       </c>
     </row>
-    <row r="17" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>54.116666666666667</v>
       </c>
@@ -10177,572 +10141,572 @@
         <v>55.4</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H17" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="I17" s="25" t="s">
         <v>489</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>490</v>
       </c>
       <c r="J17" s="4">
         <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32">
+      <c r="A18" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4">
         <v>489</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="40"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="40"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="40"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="40"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="40"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="40"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="40"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="38"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="40"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="40"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="33"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="33"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="33"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="33"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="33"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="33"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="33"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="33"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="37"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="33"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="33"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="33"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="33"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="33"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="33"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="33"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="33"/>
-      <c r="F64" s="33"/>
-      <c r="G64" s="33"/>
-      <c r="H64" s="33"/>
-      <c r="I64" s="33"/>
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="33"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="33"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="33"/>
-      <c r="B67" s="33"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="33"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10763,33 +10727,34 @@
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
     <col min="7" max="7" width="16.28515625" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="75"/>
+      <c r="A2" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="64"/>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="49" t="s">
+        <v>493</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="15">
         <v>45120</v>
@@ -10807,15 +10772,15 @@
         <v>294.74</v>
       </c>
       <c r="G3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6">
         <v>45120</v>
@@ -10830,15 +10795,15 @@
         <v>67.209999999999994</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6">
         <v>45120</v>
@@ -10856,12 +10821,12 @@
         <v>166.87</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6">
         <v>45120</v>
@@ -10879,12 +10844,12 @@
         <v>93.57</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="6">
         <v>45127</v>
@@ -10899,15 +10864,15 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6">
         <v>45127</v>
@@ -10922,15 +10887,15 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="6">
         <v>45146</v>
@@ -10945,15 +10910,15 @@
         <v>0</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6">
         <v>45146</v>
@@ -10968,21 +10933,21 @@
         <v>0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H14" s="52">
+      <c r="H14" s="44">
         <v>45136.865277777775</v>
       </c>
       <c r="I14">
         <v>9.2780000000000005</v>
       </c>
       <c r="L14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M14">
         <f>MIN(I14:I17)</f>
@@ -10997,7 +10962,7 @@
         <v>4.4400000000000004</v>
       </c>
       <c r="L15" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="M15">
         <f>MAX(I14:I18)</f>
@@ -11012,7 +10977,7 @@
         <v>2.3333333333333299</v>
       </c>
       <c r="L16" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M16">
         <f>AVERAGE(I14:I17)</f>
@@ -11021,7 +10986,7 @@
     </row>
     <row r="17" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L17" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M17">
         <f>MEDIAN(I13:I19)</f>
@@ -11044,45 +11009,45 @@
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="33"/>
-    <col min="6" max="6" width="9.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="33"/>
+    <col min="4" max="5" width="9.140625" style="12"/>
+    <col min="6" max="6" width="9.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" style="12"/>
     <col min="11" max="11" width="13.28515625" customWidth="1"/>
     <col min="12" max="12" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
+      <c r="C1" s="49" t="s">
+        <v>493</v>
       </c>
       <c r="D1" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="E1" s="24" t="s">
         <v>428</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="G1" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>430</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>445</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="I1" s="24" t="s">
         <v>431</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
@@ -11091,33 +11056,33 @@
         <v>0</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>439</v>
+        <v>98</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
@@ -11126,25 +11091,25 @@
         <v>0</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L3" s="4">
         <v>300</v>
@@ -11152,7 +11117,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B4" s="4">
         <v>0</v>
@@ -11171,16 +11136,16 @@
         <v>24.4</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>440</v>
+      <c r="K4" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L4" s="4">
         <v>200</v>
@@ -11188,7 +11153,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4">
         <v>0</v>
@@ -11197,27 +11162,27 @@
         <v>0</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -11233,27 +11198,27 @@
         <v>19.28</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>437</v>
-      </c>
       <c r="I6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>439</v>
+        <v>98</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>312</v>
+      <c r="A7" s="30" t="s">
+        <v>311</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
@@ -11271,27 +11236,27 @@
         <v>273.23999999999995</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>442</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K7" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L7" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>313</v>
+      <c r="A8" s="30" t="s">
+        <v>312</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
@@ -11308,21 +11273,21 @@
         <f>138.03/(1-(L8/L7))</f>
         <v>230.05</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <f>154.01/(1-(L8/L7))</f>
         <v>256.68333333333334</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>444</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>440</v>
+        <v>315</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L8" s="4">
         <v>200</v>
@@ -11330,7 +11295,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -11349,18 +11314,18 @@
         <v>146.46</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
@@ -11369,33 +11334,33 @@
         <v>0</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>439</v>
+        <v>98</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B11" s="4">
         <v>0</v>
@@ -11404,25 +11369,25 @@
         <v>0</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L11" s="4">
         <v>300</v>
@@ -11430,7 +11395,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B12" s="4">
         <v>0</v>
@@ -11439,25 +11404,25 @@
         <v>0</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>440</v>
+        <v>98</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L12" s="4">
         <v>200</v>
@@ -11465,7 +11430,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B13" s="4">
         <v>0</v>
@@ -11474,62 +11439,62 @@
         <v>0</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" s="4">
+        <v>0</v>
+      </c>
+      <c r="C14" s="18">
+        <v>0</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
         <v>319</v>
-      </c>
-      <c r="B14" s="4">
-        <v>0</v>
-      </c>
-      <c r="C14" s="18">
-        <v>0</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>321</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
-        <v>320</v>
       </c>
       <c r="B15" s="4">
         <v>1</v>
@@ -11547,27 +11512,27 @@
         <v>425.49</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>322</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L15" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="31" t="s">
-        <v>321</v>
+      <c r="A16" s="30" t="s">
+        <v>320</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
@@ -11589,16 +11554,16 @@
         <v>463.82</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>440</v>
+      <c r="K16" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L16" s="4">
         <v>100</v>
@@ -11606,36 +11571,36 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0</v>
+      </c>
+      <c r="C17" s="18">
+        <v>0</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
         <v>325</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
-      <c r="C17" s="18">
-        <v>0</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="I17" s="25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
-        <v>326</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
@@ -11657,24 +11622,24 @@
         <v>278.58</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="L18" s="29" t="s">
-        <v>439</v>
+      <c r="K18" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="L18" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B19" s="4">
         <v>0</v>
@@ -11683,25 +11648,25 @@
         <v>0</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L19" s="4">
         <v>400</v>
@@ -11709,7 +11674,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B20" s="4">
         <v>0</v>
@@ -11718,25 +11683,25 @@
         <v>0</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>440</v>
+        <v>98</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L20" s="4">
         <v>200</v>
@@ -11744,7 +11709,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B21" s="4">
         <v>0</v>
@@ -11753,62 +11718,62 @@
         <v>0</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="18">
+        <v>0</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="B22" s="4">
-        <v>0</v>
-      </c>
-      <c r="C22" s="18">
-        <v>0</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>332</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>439</v>
+      <c r="L22" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
-        <v>332</v>
+      <c r="A23" s="30" t="s">
+        <v>331</v>
       </c>
       <c r="B23" s="4">
         <v>1</v>
@@ -11817,37 +11782,37 @@
         <f>AVERAGE(D23:F23)</f>
         <v>360.625</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <f>141.11/(1-(L24/L23))</f>
         <v>352.77500000000003</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="29">
         <f>144.73/(1-(L24/L23))</f>
         <v>361.82499999999993</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="29">
         <f>146.91/(1-(L24/L23))</f>
         <v>367.27499999999998</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="K23" s="28" t="s">
-        <v>438</v>
+      <c r="K23" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L23" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
-        <v>333</v>
+      <c r="A24" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="B24" s="4">
         <v>1</v>
@@ -11856,37 +11821,37 @@
         <f t="shared" ref="C24:C28" si="0">AVERAGE(D24:F24)</f>
         <v>267.33333333333326</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="29">
         <f>107.02/(1-(L28/L27))</f>
         <v>267.54999999999995</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="29">
         <f>103.39/(1-(L28/L27))</f>
         <v>258.47499999999997</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="29">
         <f>110.39/(1-(L28/L27))</f>
         <v>275.97499999999997</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>440</v>
+      <c r="K24" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L24" s="4">
         <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
-        <v>334</v>
+      <c r="A25" s="30" t="s">
+        <v>333</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
@@ -11895,31 +11860,31 @@
         <f t="shared" si="0"/>
         <v>139.08333333333334</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="29">
         <f>83.49/(1-(L32/L31))</f>
         <v>139.15</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="29">
         <f>83.17/(1-(L32/L31))</f>
         <v>138.61666666666667</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="29">
         <f>83.69/(1-(L32/L31))</f>
         <v>139.48333333333335</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="I25" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>337</v>
-      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
-        <v>335</v>
+      <c r="A26" s="30" t="s">
+        <v>334</v>
       </c>
       <c r="B26" s="4">
         <v>1</v>
@@ -11928,37 +11893,37 @@
         <f t="shared" si="0"/>
         <v>133.66666666666666</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <f>106.74/(1-(L36/L35))</f>
         <v>133.42499999999998</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <f>104.9/(1-(L36/L35))</f>
         <v>131.125</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="29">
         <f>109.16/(1-(L36/L35))</f>
         <v>136.44999999999999</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="I26" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>439</v>
+      <c r="K26" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="L26" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B27" s="4">
         <v>0</v>
@@ -11977,16 +11942,16 @@
         <v>82.57</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="I27" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="K27" s="28" t="s">
-        <v>438</v>
+      <c r="K27" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L27" s="4">
         <v>500</v>
@@ -11994,7 +11959,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B28" s="4">
         <v>0</v>
@@ -12013,16 +11978,16 @@
         <v>79.47</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="K28" s="28" t="s">
-        <v>440</v>
+      <c r="K28" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L28" s="4">
         <v>300</v>
@@ -12030,7 +11995,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B29" s="4">
         <v>0</v>
@@ -12039,27 +12004,27 @@
         <v>0</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B30" s="4">
         <v>0</v>
@@ -12068,33 +12033,33 @@
         <v>0</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>439</v>
+        <v>98</v>
+      </c>
+      <c r="K30" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B31" s="4">
         <v>0</v>
@@ -12103,25 +12068,25 @@
         <v>0</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K31" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L31" s="4">
         <v>500</v>
@@ -12129,7 +12094,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B32" s="4">
         <v>0</v>
@@ -12148,24 +12113,24 @@
         <v>204.33</v>
       </c>
       <c r="G32" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="I32" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="K32" s="28" t="s">
-        <v>440</v>
+      <c r="K32" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L32" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
-        <v>343</v>
+      <c r="A33" s="30" t="s">
+        <v>342</v>
       </c>
       <c r="B33" s="4">
         <v>1</v>
@@ -12187,18 +12152,18 @@
         <v>373.66</v>
       </c>
       <c r="G33" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="I33" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B34" s="4">
         <v>0</v>
@@ -12217,24 +12182,24 @@
         <v>219.5</v>
       </c>
       <c r="G34" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="I34" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="K34" s="29" t="s">
-        <v>335</v>
-      </c>
-      <c r="L34" s="29" t="s">
-        <v>439</v>
+      <c r="K34" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="L34" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B35" s="4">
         <v>0</v>
@@ -12253,16 +12218,16 @@
         <v>190.38</v>
       </c>
       <c r="G35" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="I35" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="K35" s="28" t="s">
-        <v>438</v>
+      <c r="K35" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L35" s="4">
         <v>500</v>
@@ -12270,7 +12235,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B36" s="4">
         <v>0</v>
@@ -12289,16 +12254,16 @@
         <v>103.1</v>
       </c>
       <c r="G36" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="I36" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="K36" s="28" t="s">
-        <v>440</v>
+      <c r="K36" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L36" s="4">
         <v>100</v>
@@ -12306,7 +12271,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B37" s="4">
         <v>0</v>
@@ -12325,18 +12290,18 @@
         <v>91.84</v>
       </c>
       <c r="G37" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="I37" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B38" s="4">
         <v>0</v>
@@ -12355,24 +12320,24 @@
         <v>32.14</v>
       </c>
       <c r="G38" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="K38" s="29" t="s">
-        <v>343</v>
-      </c>
-      <c r="L38" s="29" t="s">
-        <v>439</v>
+      <c r="K38" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="L38" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B39" s="4">
         <v>0</v>
@@ -12381,25 +12346,25 @@
         <v>0</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I39" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K39" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L39" s="4">
         <v>400</v>
@@ -12407,7 +12372,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B40" s="4">
         <v>0</v>
@@ -12426,16 +12391,16 @@
         <v>40.69</v>
       </c>
       <c r="G40" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H40" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="I40" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="K40" s="28" t="s">
-        <v>440</v>
+      <c r="K40" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L40" s="4">
         <v>200</v>
@@ -12443,7 +12408,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
@@ -12452,62 +12417,62 @@
         <v>0</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B42" s="4">
+        <v>0</v>
+      </c>
+      <c r="C42" s="18">
+        <v>0</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="H42" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I42" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="K42" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="B42" s="4">
-        <v>0</v>
-      </c>
-      <c r="C42" s="18">
-        <v>0</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F42" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="G42" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="I42" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K42" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="L42" s="29" t="s">
-        <v>439</v>
+      <c r="L42" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="31" t="s">
-        <v>357</v>
+      <c r="A43" s="30" t="s">
+        <v>356</v>
       </c>
       <c r="B43" s="4">
         <v>1</v>
@@ -12529,16 +12494,16 @@
         <v>845.92</v>
       </c>
       <c r="G43" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="I43" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="K43" s="28" t="s">
-        <v>438</v>
+      <c r="K43" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L43" s="4">
         <v>400</v>
@@ -12546,7 +12511,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B44" s="4">
         <v>0</v>
@@ -12565,24 +12530,24 @@
         <v>121.08</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="K44" s="28" t="s">
-        <v>440</v>
+      <c r="K44" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L44" s="4">
         <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="31" t="s">
-        <v>359</v>
+      <c r="A45" s="30" t="s">
+        <v>358</v>
       </c>
       <c r="B45" s="4">
         <v>1</v>
@@ -12604,18 +12569,18 @@
         <v>631.04</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>403</v>
-      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
-        <v>360</v>
+      <c r="A46" s="30" t="s">
+        <v>359</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
@@ -12637,24 +12602,24 @@
         <v>915.04</v>
       </c>
       <c r="G46" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="I46" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="K46" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="L46" s="29" t="s">
-        <v>439</v>
+      <c r="K46" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="L46" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="31" t="s">
-        <v>361</v>
+      <c r="A47" s="30" t="s">
+        <v>360</v>
       </c>
       <c r="B47" s="4">
         <v>1</v>
@@ -12676,24 +12641,24 @@
         <v>578.29999999999995</v>
       </c>
       <c r="G47" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="H47" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="I47" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="K47" s="28" t="s">
-        <v>438</v>
+      <c r="K47" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L47" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="31" t="s">
-        <v>362</v>
+      <c r="A48" s="30" t="s">
+        <v>361</v>
       </c>
       <c r="B48" s="4">
         <v>1</v>
@@ -12715,16 +12680,16 @@
         <v>578.29999999999995</v>
       </c>
       <c r="G48" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="I48" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="K48" s="28" t="s">
-        <v>440</v>
+      <c r="K48" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L48" s="4">
         <v>300</v>
@@ -12732,7 +12697,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B49" s="4">
         <v>0</v>
@@ -12754,18 +12719,18 @@
         <v>122.95</v>
       </c>
       <c r="G49" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="H49" s="4" t="s">
+      <c r="I49" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" s="4">
         <v>0</v>
@@ -12774,33 +12739,33 @@
         <v>0</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H50" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I50" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K50" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="L50" s="29" t="s">
-        <v>439</v>
+        <v>98</v>
+      </c>
+      <c r="K50" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="L50" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B51" s="4">
         <v>0</v>
@@ -12809,25 +12774,25 @@
         <v>0</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H51" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I51" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K51" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L51" s="4">
         <v>400</v>
@@ -12835,7 +12800,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B52" s="4">
         <v>0</v>
@@ -12844,33 +12809,33 @@
         <v>0</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I52" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K52" s="28" t="s">
-        <v>440</v>
+        <v>98</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L52" s="4">
         <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="31" t="s">
-        <v>367</v>
+      <c r="A53" s="30" t="s">
+        <v>366</v>
       </c>
       <c r="B53" s="4">
         <v>1</v>
@@ -12892,18 +12857,18 @@
         <v>491.26</v>
       </c>
       <c r="G53" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="H53" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="I53" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>418</v>
-      </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
-        <v>368</v>
+      <c r="A54" s="30" t="s">
+        <v>367</v>
       </c>
       <c r="B54" s="4">
         <v>1</v>
@@ -12912,37 +12877,37 @@
         <f t="shared" ref="C54:C56" si="3">AVERAGE(D54:F54)</f>
         <v>290.97777777777782</v>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="29">
         <f>167.02/(1-(L68/L67))</f>
         <v>278.36666666666667</v>
       </c>
-      <c r="E54" s="30">
+      <c r="E54" s="29">
         <f>171.84/(1-(L68/L67))</f>
         <v>286.40000000000003</v>
       </c>
-      <c r="F54" s="30">
+      <c r="F54" s="29">
         <f>184.9/(1-(L68/L67))</f>
         <v>308.16666666666669</v>
       </c>
       <c r="G54" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="K54" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="L54" s="29" t="s">
-        <v>439</v>
+      <c r="K54" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="L54" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B55" s="4">
         <v>0</v>
@@ -12961,16 +12926,16 @@
         <v>242.57</v>
       </c>
       <c r="G55" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="H55" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="I55" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="K55" s="28" t="s">
-        <v>438</v>
+      <c r="K55" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L55" s="4">
         <v>400</v>
@@ -12978,7 +12943,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B56" s="4">
         <v>0</v>
@@ -12997,16 +12962,16 @@
         <v>191.22</v>
       </c>
       <c r="G56" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="H56" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="I56" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="K56" s="28" t="s">
-        <v>440</v>
+      <c r="K56" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L56" s="4">
         <v>200</v>
@@ -13014,7 +12979,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B57" s="4">
         <v>0</v>
@@ -13033,18 +12998,18 @@
         <v>132.82</v>
       </c>
       <c r="G57" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="H57" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="I57" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B58" s="4">
         <v>0</v>
@@ -13063,24 +13028,24 @@
         <v>103.48</v>
       </c>
       <c r="G58" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="H58" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="I58" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="K58" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="L58" s="29" t="s">
-        <v>439</v>
+      <c r="K58" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="L58" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="32" t="s">
-        <v>385</v>
+      <c r="A59" s="4" t="s">
+        <v>384</v>
       </c>
       <c r="B59" s="4">
         <v>0</v>
@@ -13089,25 +13054,25 @@
         <v>0</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H59" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I59" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K59" s="28" t="s">
-        <v>438</v>
+        <v>98</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L59" s="4">
         <v>400</v>
@@ -13115,7 +13080,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B60" s="4">
         <v>0</v>
@@ -13124,25 +13089,25 @@
         <v>0</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H60" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K60" s="28" t="s">
-        <v>440</v>
+        <v>98</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L60" s="4">
         <v>200</v>
@@ -13150,7 +13115,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B61" s="4">
         <v>0</v>
@@ -13159,27 +13124,27 @@
         <v>0</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H61" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B62" s="4">
         <v>1</v>
@@ -13201,24 +13166,24 @@
         <v>327.82</v>
       </c>
       <c r="G62" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="H62" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="I62" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="K62" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="L62" s="29" t="s">
-        <v>439</v>
+      <c r="K62" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="L62" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B63" s="4">
         <v>0</v>
@@ -13237,16 +13202,16 @@
         <v>228.79</v>
       </c>
       <c r="G63" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="H63" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="I63" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="K63" s="28" t="s">
-        <v>438</v>
+      <c r="K63" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L63" s="4">
         <v>400</v>
@@ -13254,7 +13219,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B64" s="4">
         <v>0</v>
@@ -13273,16 +13238,16 @@
         <v>207.15</v>
       </c>
       <c r="G64" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="I64" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="K64" s="28" t="s">
-        <v>440</v>
+      <c r="K64" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L64" s="4">
         <v>200</v>
@@ -13290,7 +13255,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B65" s="4">
         <v>0</v>
@@ -13309,18 +13274,18 @@
         <v>133.51</v>
       </c>
       <c r="G65" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="H65" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="H65" s="25" t="s">
+      <c r="I65" s="25" t="s">
         <v>384</v>
-      </c>
-      <c r="I65" s="25" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B66" s="4">
         <v>0</v>
@@ -13339,24 +13304,24 @@
         <v>88.41</v>
       </c>
       <c r="G66" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="I66" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="K66" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="L66" s="29" t="s">
-        <v>439</v>
+      <c r="K66" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="L66" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B67" s="4">
         <v>0</v>
@@ -13375,48 +13340,48 @@
         <v>60.39</v>
       </c>
       <c r="G67" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="H67" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="H67" s="4" t="s">
+      <c r="I67" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="I67" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="K67" s="28" t="s">
-        <v>438</v>
+      <c r="K67" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L67" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K68" s="28" t="s">
-        <v>440</v>
+      <c r="K68" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L68" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K70" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="L70" s="29" t="s">
-        <v>439</v>
+      <c r="K70" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="L70" s="28" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K71" s="28" t="s">
-        <v>438</v>
+      <c r="K71" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="L71" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="K72" s="28" t="s">
-        <v>440</v>
+      <c r="K72" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="L72" s="4">
         <v>200</v>
